--- a/data/cyntec_inductor_data.xlsx
+++ b/data/cyntec_inductor_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://renesasgroup-my.sharepoint.com/personal/gary_kidwell_wz_renesas_com/Documents/python/charger/mathmodels/pdis_2or3lvl_bb/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="803" documentId="11_88A5EEC595FCDE19E65C93C75DD0486FD8C93E14" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{160B5F0C-4B7F-4577-AABA-9F5AB12CA9CB}"/>
+  <xr:revisionPtr revIDLastSave="825" documentId="11_88A5EEC595FCDE19E65C93C75DD0486FD8C93E14" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D6DCF0E-86A3-46A6-8FCA-F55B26DF33DD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="772" firstSheet="11" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29910" yWindow="1620" windowWidth="21000" windowHeight="12735" tabRatio="772" firstSheet="11" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="htel20121b" sheetId="21" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="39">
   <si>
     <t>Lout</t>
   </si>
@@ -2138,7 +2138,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40693CA2-7319-4057-AD3C-7C4101A3AA7E}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -2190,30 +2190,30 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>2.2000000000000002</v>
+        <v>0.47</v>
       </c>
       <c r="B2">
-        <v>1.0699999999999999E-2</v>
+        <v>2E-3</v>
       </c>
       <c r="C2">
-        <v>11.5</v>
+        <v>24</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2">
-        <f t="shared" ref="E2" si="0">40/F2</f>
-        <v>24.580046072223862</v>
+        <f t="shared" ref="E2:E4" si="0">40/F2</f>
+        <v>30.193236714975846</v>
       </c>
       <c r="F2" s="1">
-        <f t="shared" ref="F2" si="1">C2^2*B2*1.15</f>
-        <v>1.6273362499999997</v>
-      </c>
-      <c r="G2">
-        <v>1.3499999999999999E-5</v>
-      </c>
-      <c r="H2">
-        <v>1.3480000000000001E-2</v>
+        <f t="shared" ref="F2:F4" si="1">C2^2*B2*1.15</f>
+        <v>1.3248</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1.489E-5</v>
+      </c>
+      <c r="H2" s="3">
+        <v>6.3949999999999996E-3</v>
       </c>
       <c r="I2">
         <v>1.254</v>
@@ -2231,6 +2231,98 @@
         <v>6.8</v>
       </c>
       <c r="N2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>0.68</v>
+      </c>
+      <c r="B3">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="C3">
+        <v>20.7</v>
+      </c>
+      <c r="D3">
+        <v>25.5</v>
+      </c>
+      <c r="E3" s="2">
+        <f t="shared" si="0"/>
+        <v>30.064756855600741</v>
+      </c>
+      <c r="F3" s="1">
+        <f t="shared" si="1"/>
+        <v>1.3304614499999998</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.3159999999999999E-5</v>
+      </c>
+      <c r="H3" s="3">
+        <v>9.3860000000000002E-3</v>
+      </c>
+      <c r="I3">
+        <v>1.254</v>
+      </c>
+      <c r="J3">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3">
+        <v>8.4</v>
+      </c>
+      <c r="M3">
+        <v>6.8</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="C4">
+        <v>11.5</v>
+      </c>
+      <c r="D4">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" si="0"/>
+        <v>24.580046072223862</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" si="1"/>
+        <v>1.6273362499999997</v>
+      </c>
+      <c r="G4">
+        <v>1.3499999999999999E-5</v>
+      </c>
+      <c r="H4">
+        <v>1.3480000000000001E-2</v>
+      </c>
+      <c r="I4">
+        <v>1.254</v>
+      </c>
+      <c r="J4">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4">
+        <v>8.4</v>
+      </c>
+      <c r="M4">
+        <v>6.8</v>
+      </c>
+      <c r="N4">
         <v>3</v>
       </c>
     </row>

--- a/data/cyntec_inductor_data.xlsx
+++ b/data/cyntec_inductor_data.xlsx
@@ -1,43 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://renesasgroup-my.sharepoint.com/personal/gary_kidwell_wz_renesas_com/Documents/python/charger/mathmodels/pdis_2or3lvl_bb/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="825" documentId="11_88A5EEC595FCDE19E65C93C75DD0486FD8C93E14" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D6DCF0E-86A3-46A6-8FCA-F55B26DF33DD}"/>
+  <xr:revisionPtr revIDLastSave="945" documentId="11_88A5EEC595FCDE19E65C93C75DD0486FD8C93E14" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54F733BC-4F29-4BD2-929C-B9B0FDC20F66}"/>
   <bookViews>
-    <workbookView xWindow="29910" yWindow="1620" windowWidth="21000" windowHeight="12735" tabRatio="772" firstSheet="11" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1560" windowWidth="24270" windowHeight="13695" tabRatio="772" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="htel20121b" sheetId="21" r:id="rId1"/>
     <sheet name="htep32251b" sheetId="22" r:id="rId2"/>
     <sheet name="htey030S" sheetId="19" r:id="rId3"/>
     <sheet name="hbeq031b" sheetId="20" r:id="rId4"/>
-    <sheet name="cmle051e" sheetId="13" r:id="rId5"/>
-    <sheet name="cmle051h" sheetId="14" r:id="rId6"/>
-    <sheet name="hbed053t" sheetId="16" r:id="rId7"/>
-    <sheet name="pimb053t" sheetId="12" r:id="rId8"/>
-    <sheet name="cmlb053t" sheetId="5" r:id="rId9"/>
-    <sheet name="cmle061b" sheetId="9" r:id="rId10"/>
-    <sheet name="cmle061e" sheetId="10" r:id="rId11"/>
-    <sheet name="cmle062t" sheetId="8" r:id="rId12"/>
-    <sheet name="cmls062d" sheetId="15" r:id="rId13"/>
-    <sheet name="cmlb063t" sheetId="6" r:id="rId14"/>
-    <sheet name="cmle063t" sheetId="2" r:id="rId15"/>
-    <sheet name="hbed063t" sheetId="18" r:id="rId16"/>
-    <sheet name="cmll063t" sheetId="17" r:id="rId17"/>
-    <sheet name="pimb063t" sheetId="11" r:id="rId18"/>
-    <sheet name="cmle064t" sheetId="24" r:id="rId19"/>
-    <sheet name="cmle083t" sheetId="27" r:id="rId20"/>
-    <sheet name="cmle103t" sheetId="25" r:id="rId21"/>
-    <sheet name="cmle104t" sheetId="26" r:id="rId22"/>
-    <sheet name="cmlb104t" sheetId="4" r:id="rId23"/>
-    <sheet name="cmle105t" sheetId="28" r:id="rId24"/>
-    <sheet name="cmls135t" sheetId="23" r:id="rId25"/>
+    <sheet name="hbed042t" sheetId="31" r:id="rId5"/>
+    <sheet name="hbed043t" sheetId="34" r:id="rId6"/>
+    <sheet name="cmle051e" sheetId="13" r:id="rId7"/>
+    <sheet name="cmle051h" sheetId="14" r:id="rId8"/>
+    <sheet name="hbed052d" sheetId="29" r:id="rId9"/>
+    <sheet name="hbed053t" sheetId="16" r:id="rId10"/>
+    <sheet name="pimb053t" sheetId="12" r:id="rId11"/>
+    <sheet name="cmlb053t" sheetId="5" r:id="rId12"/>
+    <sheet name="cmle061b" sheetId="9" r:id="rId13"/>
+    <sheet name="cmle061e" sheetId="10" r:id="rId14"/>
+    <sheet name="cmle062t" sheetId="8" r:id="rId15"/>
+    <sheet name="cmls062d" sheetId="15" r:id="rId16"/>
+    <sheet name="cmlb063t" sheetId="6" r:id="rId17"/>
+    <sheet name="cmle063t" sheetId="2" r:id="rId18"/>
+    <sheet name="hbed062d" sheetId="30" r:id="rId19"/>
+    <sheet name="hbed063t" sheetId="18" r:id="rId20"/>
+    <sheet name="cmll063t" sheetId="17" r:id="rId21"/>
+    <sheet name="pimb063t" sheetId="11" r:id="rId22"/>
+    <sheet name="cmle064t" sheetId="24" r:id="rId23"/>
+    <sheet name="cmle083t" sheetId="27" r:id="rId24"/>
+    <sheet name="cmle102d" sheetId="32" r:id="rId25"/>
+    <sheet name="cmle103t" sheetId="25" r:id="rId26"/>
+    <sheet name="pimb103t" sheetId="33" r:id="rId27"/>
+    <sheet name="cmle104t" sheetId="26" r:id="rId28"/>
+    <sheet name="cmlb104t" sheetId="4" r:id="rId29"/>
+    <sheet name="cmle105t" sheetId="28" r:id="rId30"/>
+    <sheet name="cmls135t" sheetId="23" r:id="rId31"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="45">
   <si>
     <t>Lout</t>
   </si>
@@ -174,6 +180,24 @@
   </si>
   <si>
     <t>cmle105t</t>
+  </si>
+  <si>
+    <t>hbed062d</t>
+  </si>
+  <si>
+    <t>hbed052d</t>
+  </si>
+  <si>
+    <t>hbed042t</t>
+  </si>
+  <si>
+    <t>cmle102d</t>
+  </si>
+  <si>
+    <t>pimb103t</t>
+  </si>
+  <si>
+    <t>hbed043t</t>
   </si>
 </sst>
 </file>
@@ -642,6 +666,879 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B931419B-A406-4BFE-8A46-5F910D217C80}">
+  <dimension ref="A1:N11"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="B2">
+        <v>8.4999999999999995E-4</v>
+      </c>
+      <c r="C2">
+        <v>38</v>
+      </c>
+      <c r="D2">
+        <v>45</v>
+      </c>
+      <c r="E2">
+        <f>40/F2</f>
+        <v>28.338446061310236</v>
+      </c>
+      <c r="F2">
+        <f>C2^2*B2*1.15</f>
+        <v>1.4115099999999996</v>
+      </c>
+      <c r="G2">
+        <f>0.00000957</f>
+        <v>9.5699999999999999E-6</v>
+      </c>
+      <c r="H2">
+        <v>5.1599999999999997E-3</v>
+      </c>
+      <c r="I2">
+        <v>1.254</v>
+      </c>
+      <c r="J2">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2">
+        <v>5.5</v>
+      </c>
+      <c r="M2">
+        <v>5.7</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
+        <v>0.33</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1.8E-3</v>
+      </c>
+      <c r="C3">
+        <v>28.5</v>
+      </c>
+      <c r="D3">
+        <v>32</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E11" si="0">40/F3</f>
+        <v>23.790300397149334</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F11" si="1">C3^2*B3*1.15</f>
+        <v>1.6813574999999996</v>
+      </c>
+      <c r="G3">
+        <f>0.0000096</f>
+        <v>9.5999999999999996E-6</v>
+      </c>
+      <c r="H3">
+        <v>6.7799999999999996E-3</v>
+      </c>
+      <c r="I3">
+        <v>1.254</v>
+      </c>
+      <c r="J3">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>5.5</v>
+      </c>
+      <c r="M3">
+        <v>5.7</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>0.36</v>
+      </c>
+      <c r="B4">
+        <v>2E-3</v>
+      </c>
+      <c r="C4">
+        <v>27</v>
+      </c>
+      <c r="D4">
+        <v>29</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>23.856384564919189</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>1.6766999999999999</v>
+      </c>
+      <c r="G4">
+        <f>0.00000983</f>
+        <v>9.8300000000000008E-6</v>
+      </c>
+      <c r="H4">
+        <v>6.9899999999999997E-3</v>
+      </c>
+      <c r="I4">
+        <v>1.254</v>
+      </c>
+      <c r="J4">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4">
+        <v>5.5</v>
+      </c>
+      <c r="M4">
+        <v>5.7</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>0.47</v>
+      </c>
+      <c r="B5">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="C5">
+        <v>24</v>
+      </c>
+      <c r="D5">
+        <v>26</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>24.154589371980677</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>1.6559999999999999</v>
+      </c>
+      <c r="G5">
+        <f>0.00000883</f>
+        <v>8.8300000000000002E-6</v>
+      </c>
+      <c r="H5">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="I5">
+        <v>1.254</v>
+      </c>
+      <c r="J5">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5">
+        <v>5.5</v>
+      </c>
+      <c r="M5">
+        <v>5.7</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="B6">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>23.95496466642712</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>1.6697999999999997</v>
+      </c>
+      <c r="G6">
+        <f>0.00000921</f>
+        <v>9.2099999999999999E-6</v>
+      </c>
+      <c r="H6">
+        <v>1.03E-2</v>
+      </c>
+      <c r="I6">
+        <v>1.254</v>
+      </c>
+      <c r="J6">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6">
+        <v>5.5</v>
+      </c>
+      <c r="M6">
+        <v>5.7</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="B7">
+        <v>3.8E-3</v>
+      </c>
+      <c r="C7">
+        <v>19.5</v>
+      </c>
+      <c r="D7">
+        <v>21.5</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>24.07184241368364</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>1.6616924999999998</v>
+      </c>
+      <c r="G7">
+        <f>0.00000871</f>
+        <v>8.7099999999999996E-6</v>
+      </c>
+      <c r="H7">
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="I7">
+        <v>1.254</v>
+      </c>
+      <c r="J7">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7">
+        <v>5.5</v>
+      </c>
+      <c r="M7">
+        <v>5.7</v>
+      </c>
+      <c r="N7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C8">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>18</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>24.071009477959983</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>1.6617499999999998</v>
+      </c>
+      <c r="G8">
+        <f>0.00000872</f>
+        <v>8.7199999999999995E-6</v>
+      </c>
+      <c r="H8">
+        <v>1.2200000000000001E-2</v>
+      </c>
+      <c r="I8">
+        <v>1.254</v>
+      </c>
+      <c r="J8">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8">
+        <v>5.5</v>
+      </c>
+      <c r="M8">
+        <v>5.7</v>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="B9">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="C9">
+        <v>14</v>
+      </c>
+      <c r="D9">
+        <v>15</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>24.647540175490487</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>1.6228799999999999</v>
+      </c>
+      <c r="G9">
+        <f>0.000008982</f>
+        <v>8.9819999999999997E-6</v>
+      </c>
+      <c r="H9">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="I9">
+        <v>1.254</v>
+      </c>
+      <c r="J9">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9">
+        <v>5.5</v>
+      </c>
+      <c r="M9">
+        <v>5.7</v>
+      </c>
+      <c r="N9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="C10">
+        <v>12</v>
+      </c>
+      <c r="D10">
+        <v>11</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>24.647540175490487</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>1.6228799999999999</v>
+      </c>
+      <c r="G10">
+        <f>0.00000891</f>
+        <v>8.9099999999999994E-6</v>
+      </c>
+      <c r="H10">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="I10">
+        <v>1.254</v>
+      </c>
+      <c r="J10">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10">
+        <v>5.5</v>
+      </c>
+      <c r="M10">
+        <v>5.7</v>
+      </c>
+      <c r="N10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="B11">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>23.188405797101453</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>1.7249999999999999</v>
+      </c>
+      <c r="G11">
+        <f>0.00000885</f>
+        <v>8.85E-6</v>
+      </c>
+      <c r="H11">
+        <v>2.3199999999999998E-2</v>
+      </c>
+      <c r="I11">
+        <v>1.254</v>
+      </c>
+      <c r="J11">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K11" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11">
+        <v>5.5</v>
+      </c>
+      <c r="M11">
+        <v>5.7</v>
+      </c>
+      <c r="N11">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A5FAB1-3D42-4172-B790-7D8771165FE4}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="C2">
+        <v>8.5</v>
+      </c>
+      <c r="D2">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <f>40/F2</f>
+        <v>37.032322273784594</v>
+      </c>
+      <c r="F2">
+        <f>C2^2*B2*1.15</f>
+        <v>1.0801374999999998</v>
+      </c>
+      <c r="G2">
+        <f>0.000669</f>
+        <v>6.69E-4</v>
+      </c>
+      <c r="H2">
+        <v>1.4370000000000001E-2</v>
+      </c>
+      <c r="I2">
+        <v>1.028</v>
+      </c>
+      <c r="J2">
+        <v>2.5179999999999998</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2">
+        <v>7</v>
+      </c>
+      <c r="M2">
+        <v>4.7</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F45A2FD-4FF8-4DE7-9D64-03112843A7F5}">
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="B2">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="C2">
+        <v>11</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2">
+        <f t="shared" ref="E2:E5" si="0">40/F2</f>
+        <v>35.932446999640675</v>
+      </c>
+      <c r="F2" s="1">
+        <f t="shared" ref="F2:F5" si="1">C2^2*B2*1.15</f>
+        <v>1.1132</v>
+      </c>
+      <c r="G2">
+        <f>0.000714</f>
+        <v>7.1400000000000001E-4</v>
+      </c>
+      <c r="H2">
+        <v>9.5600000000000008E-3</v>
+      </c>
+      <c r="I2">
+        <v>1.028</v>
+      </c>
+      <c r="J2">
+        <v>2.5179999999999998</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2">
+        <v>7</v>
+      </c>
+      <c r="M2">
+        <v>4.7</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>0.68</v>
+      </c>
+      <c r="B3">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="C3">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>11.5</v>
+      </c>
+      <c r="E3" s="2">
+        <f t="shared" si="0"/>
+        <v>35.932446999640675</v>
+      </c>
+      <c r="F3" s="1">
+        <f t="shared" si="1"/>
+        <v>1.1132</v>
+      </c>
+      <c r="G3">
+        <f>0.000715</f>
+        <v>7.1500000000000003E-4</v>
+      </c>
+      <c r="H3">
+        <v>1.06E-2</v>
+      </c>
+      <c r="I3">
+        <v>1.028</v>
+      </c>
+      <c r="J3">
+        <v>2.5179999999999998</v>
+      </c>
+      <c r="K3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4.7</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="C4">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" si="0"/>
+        <v>34.492184502144113</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" si="1"/>
+        <v>1.1596830000000002</v>
+      </c>
+      <c r="G4">
+        <f>0.000642</f>
+        <v>6.4199999999999999E-4</v>
+      </c>
+      <c r="H4">
+        <v>1.465E-2</v>
+      </c>
+      <c r="I4">
+        <v>1.028</v>
+      </c>
+      <c r="J4">
+        <v>2.5179999999999998</v>
+      </c>
+      <c r="K4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4">
+        <v>7</v>
+      </c>
+      <c r="M4">
+        <v>4.7</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1.5</v>
+      </c>
+      <c r="B5">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="C5">
+        <v>7.8</v>
+      </c>
+      <c r="D5">
+        <v>8.6</v>
+      </c>
+      <c r="E5" s="2">
+        <f t="shared" si="0"/>
+        <v>33.629779842646258</v>
+      </c>
+      <c r="F5" s="1">
+        <f t="shared" si="1"/>
+        <v>1.189422</v>
+      </c>
+      <c r="G5">
+        <f>0.000657</f>
+        <v>6.5700000000000003E-4</v>
+      </c>
+      <c r="H5">
+        <v>1.562E-2</v>
+      </c>
+      <c r="I5">
+        <v>1.028</v>
+      </c>
+      <c r="J5">
+        <v>2.5179999999999998</v>
+      </c>
+      <c r="K5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
+        <v>4.7</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8213006-9952-428D-8BC6-3F226A0269EB}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -792,7 +1689,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3B95D26-706C-492F-A2B4-D5602699B03D}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -943,7 +1840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9947CF10-DCB3-444E-AA0E-E9C95D47B18D}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -1094,7 +1991,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6BC391-7CE4-427C-A1D0-C3A0CD4B07F8}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -1192,7 +2089,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{993A6BDF-C8EC-4A56-8A8C-7D4D9FABD0E6}">
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -1386,7 +2283,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019AFF8E-C5B7-433D-B580-B909E8C2DFC6}">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -2136,9 +3033,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40693CA2-7319-4057-AD3C-7C4101A3AA7E}">
-  <dimension ref="A1:N4"/>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{546D74C1-6195-4039-B02D-05C9ABC466CC}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -2190,30 +3087,30 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="B2">
-        <v>2E-3</v>
+        <v>2.3E-3</v>
       </c>
       <c r="C2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2">
-        <f t="shared" ref="E2:E4" si="0">40/F2</f>
-        <v>30.193236714975846</v>
+        <f t="shared" ref="E2" si="0">40/F2</f>
+        <v>24.196597353497165</v>
       </c>
       <c r="F2" s="1">
-        <f t="shared" ref="F2:F4" si="1">C2^2*B2*1.15</f>
-        <v>1.3248</v>
+        <f t="shared" ref="F2" si="1">C2^2*B2*1.15</f>
+        <v>1.653125</v>
       </c>
       <c r="G2" s="3">
-        <v>1.489E-5</v>
+        <v>1.0380000000000001E-5</v>
       </c>
       <c r="H2" s="3">
-        <v>6.3949999999999996E-3</v>
+        <v>6.9470000000000001E-3</v>
       </c>
       <c r="I2">
         <v>1.254</v>
@@ -2222,7 +3119,7 @@
         <v>2.3260000000000001</v>
       </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="L2">
         <v>8.4</v>
@@ -2231,456 +3128,12 @@
         <v>6.8</v>
       </c>
       <c r="N2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>0.68</v>
-      </c>
-      <c r="B3">
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="C3">
-        <v>20.7</v>
-      </c>
-      <c r="D3">
-        <v>25.5</v>
-      </c>
-      <c r="E3" s="2">
-        <f t="shared" si="0"/>
-        <v>30.064756855600741</v>
-      </c>
-      <c r="F3" s="1">
-        <f t="shared" si="1"/>
-        <v>1.3304614499999998</v>
-      </c>
-      <c r="G3" s="3">
-        <v>1.3159999999999999E-5</v>
-      </c>
-      <c r="H3" s="3">
-        <v>9.3860000000000002E-3</v>
-      </c>
-      <c r="I3">
-        <v>1.254</v>
-      </c>
-      <c r="J3">
-        <v>2.3260000000000001</v>
-      </c>
-      <c r="K3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3">
-        <v>8.4</v>
-      </c>
-      <c r="M3">
-        <v>6.8</v>
-      </c>
-      <c r="N3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B4">
-        <v>1.0699999999999999E-2</v>
-      </c>
-      <c r="C4">
-        <v>11.5</v>
-      </c>
-      <c r="D4">
-        <v>18</v>
-      </c>
-      <c r="E4" s="2">
-        <f t="shared" si="0"/>
-        <v>24.580046072223862</v>
-      </c>
-      <c r="F4" s="1">
-        <f t="shared" si="1"/>
-        <v>1.6273362499999997</v>
-      </c>
-      <c r="G4">
-        <v>1.3499999999999999E-5</v>
-      </c>
-      <c r="H4">
-        <v>1.3480000000000001E-2</v>
-      </c>
-      <c r="I4">
-        <v>1.254</v>
-      </c>
-      <c r="J4">
-        <v>2.3260000000000001</v>
-      </c>
-      <c r="K4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4">
-        <v>8.4</v>
-      </c>
-      <c r="M4">
-        <v>6.8</v>
-      </c>
-      <c r="N4">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D56B1A3F-2BB9-4559-ACF3-D3704694A32E}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="8" max="8" width="25.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0.4</v>
-      </c>
-      <c r="B2">
-        <v>1.8699999999999999E-3</v>
-      </c>
-      <c r="C2">
-        <v>24</v>
-      </c>
-      <c r="D2">
-        <v>36</v>
-      </c>
-      <c r="E2" s="1">
-        <f>40/F2</f>
-        <v>37.136066547831255</v>
-      </c>
-      <c r="F2" s="1">
-        <f>C2^2*B2</f>
-        <v>1.0771199999999999</v>
-      </c>
-      <c r="G2">
-        <v>1.248E-4</v>
-      </c>
-      <c r="H2">
-        <v>5.391E-3</v>
-      </c>
-      <c r="I2">
-        <v>1.1011044400000001</v>
-      </c>
-      <c r="J2">
-        <v>2.2485574389999998</v>
-      </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2">
-        <v>8.4</v>
-      </c>
-      <c r="M2">
-        <v>6.8</v>
-      </c>
-      <c r="N2">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5520FBE5-C15D-498B-9A1C-8FA65C0F7F27}">
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>6.7000000000000002E-3</v>
-      </c>
-      <c r="C2">
-        <v>14</v>
-      </c>
-      <c r="D2">
-        <v>15</v>
-      </c>
-      <c r="E2">
-        <f>40/F2</f>
-        <v>26.486908845303208</v>
-      </c>
-      <c r="F2">
-        <f>C2^2*B2*1.15</f>
-        <v>1.5101800000000001</v>
-      </c>
-      <c r="G2">
-        <f>0.00142</f>
-        <v>1.42E-3</v>
-      </c>
-      <c r="H2">
-        <v>9.2300000000000004E-3</v>
-      </c>
-      <c r="I2">
-        <v>1.028</v>
-      </c>
-      <c r="J2">
-        <v>2.5179999999999998</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2">
-        <v>8.4</v>
-      </c>
-      <c r="M2">
-        <v>6.8</v>
-      </c>
-      <c r="N2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B3">
-        <v>1.35E-2</v>
-      </c>
-      <c r="C3">
-        <v>9.5</v>
-      </c>
-      <c r="D3">
-        <v>10</v>
-      </c>
-      <c r="E3">
-        <f>40/F3</f>
-        <v>28.548360476579195</v>
-      </c>
-      <c r="F3">
-        <f>C3^2*B3*1.15</f>
-        <v>1.4011312499999999</v>
-      </c>
-      <c r="G3">
-        <f>0.00143</f>
-        <v>1.4300000000000001E-3</v>
-      </c>
-      <c r="H3">
-        <v>1.3729999999999999E-2</v>
-      </c>
-      <c r="I3">
-        <v>1.028</v>
-      </c>
-      <c r="J3">
-        <v>2.5179999999999998</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3">
-        <v>8.4</v>
-      </c>
-      <c r="M3">
-        <v>6.8</v>
-      </c>
-      <c r="N3">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BC573D-AEF5-48A1-9870-479DF8E5F424}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0.42</v>
-      </c>
-      <c r="B2">
-        <v>1.5499999999999999E-3</v>
-      </c>
-      <c r="C2">
-        <v>24</v>
-      </c>
-      <c r="D2">
-        <v>23</v>
-      </c>
-      <c r="E2">
-        <f>40/F2</f>
-        <v>38.959015116097873</v>
-      </c>
-      <c r="F2">
-        <f>C2^2*B2*1.15</f>
-        <v>1.0267199999999999</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1.7699999999999999E-4</v>
-      </c>
-      <c r="H2">
-        <v>5.8300000000000001E-3</v>
-      </c>
-      <c r="I2">
-        <v>1.101</v>
-      </c>
-      <c r="J2">
-        <v>2.2490000000000001</v>
-      </c>
-      <c r="K2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2">
-        <v>8.4</v>
-      </c>
-      <c r="M2">
-        <v>6.8</v>
-      </c>
-      <c r="N2">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2790,6 +3243,600 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40693CA2-7319-4057-AD3C-7C4101A3AA7E}">
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0.47</v>
+      </c>
+      <c r="B2">
+        <v>2E-3</v>
+      </c>
+      <c r="C2">
+        <v>24</v>
+      </c>
+      <c r="D2">
+        <v>31</v>
+      </c>
+      <c r="E2" s="2">
+        <f t="shared" ref="E2:E5" si="0">40/F2</f>
+        <v>30.193236714975846</v>
+      </c>
+      <c r="F2" s="1">
+        <f t="shared" ref="F2:F5" si="1">C2^2*B2*1.15</f>
+        <v>1.3248</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1.489E-5</v>
+      </c>
+      <c r="H2" s="3">
+        <v>6.3949999999999996E-3</v>
+      </c>
+      <c r="I2">
+        <v>1.254</v>
+      </c>
+      <c r="J2">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2">
+        <v>8.4</v>
+      </c>
+      <c r="M2">
+        <v>6.8</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>0.68</v>
+      </c>
+      <c r="B3">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="C3">
+        <v>20.7</v>
+      </c>
+      <c r="D3">
+        <v>25.5</v>
+      </c>
+      <c r="E3" s="2">
+        <f t="shared" si="0"/>
+        <v>30.064756855600741</v>
+      </c>
+      <c r="F3" s="1">
+        <f t="shared" si="1"/>
+        <v>1.3304614499999998</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.3159999999999999E-5</v>
+      </c>
+      <c r="H3" s="3">
+        <v>9.3860000000000002E-3</v>
+      </c>
+      <c r="I3">
+        <v>1.254</v>
+      </c>
+      <c r="J3">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3">
+        <v>8.4</v>
+      </c>
+      <c r="M3">
+        <v>6.8</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="C4">
+        <v>18.5</v>
+      </c>
+      <c r="D4">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" si="0"/>
+        <v>22.584276403312835</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" si="1"/>
+        <v>1.7711437499999998</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.33E-5</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1.1310000000000001E-2</v>
+      </c>
+      <c r="I4">
+        <v>1.254</v>
+      </c>
+      <c r="J4">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4">
+        <v>8.4</v>
+      </c>
+      <c r="M4">
+        <v>6.8</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="C5">
+        <v>11.5</v>
+      </c>
+      <c r="D5">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2">
+        <f t="shared" si="0"/>
+        <v>24.580046072223862</v>
+      </c>
+      <c r="F5" s="1">
+        <f t="shared" si="1"/>
+        <v>1.6273362499999997</v>
+      </c>
+      <c r="G5">
+        <v>1.3499999999999999E-5</v>
+      </c>
+      <c r="H5">
+        <v>1.3480000000000001E-2</v>
+      </c>
+      <c r="I5">
+        <v>1.254</v>
+      </c>
+      <c r="J5">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5">
+        <v>8.4</v>
+      </c>
+      <c r="M5">
+        <v>6.8</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D56B1A3F-2BB9-4559-ACF3-D3704694A32E}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="8" max="8" width="25.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0.4</v>
+      </c>
+      <c r="B2">
+        <v>1.8699999999999999E-3</v>
+      </c>
+      <c r="C2">
+        <v>24</v>
+      </c>
+      <c r="D2">
+        <v>36</v>
+      </c>
+      <c r="E2" s="1">
+        <f>40/F2</f>
+        <v>37.136066547831255</v>
+      </c>
+      <c r="F2" s="1">
+        <f>C2^2*B2</f>
+        <v>1.0771199999999999</v>
+      </c>
+      <c r="G2">
+        <v>1.248E-4</v>
+      </c>
+      <c r="H2">
+        <v>5.391E-3</v>
+      </c>
+      <c r="I2">
+        <v>1.1011044400000001</v>
+      </c>
+      <c r="J2">
+        <v>2.2485574389999998</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2">
+        <v>8.4</v>
+      </c>
+      <c r="M2">
+        <v>6.8</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5520FBE5-C15D-498B-9A1C-8FA65C0F7F27}">
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="C2">
+        <v>14</v>
+      </c>
+      <c r="D2">
+        <v>15</v>
+      </c>
+      <c r="E2">
+        <f>40/F2</f>
+        <v>26.486908845303208</v>
+      </c>
+      <c r="F2">
+        <f>C2^2*B2*1.15</f>
+        <v>1.5101800000000001</v>
+      </c>
+      <c r="G2">
+        <f>0.00142</f>
+        <v>1.42E-3</v>
+      </c>
+      <c r="H2">
+        <v>9.2300000000000004E-3</v>
+      </c>
+      <c r="I2">
+        <v>1.028</v>
+      </c>
+      <c r="J2">
+        <v>2.5179999999999998</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2">
+        <v>8.4</v>
+      </c>
+      <c r="M2">
+        <v>6.8</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3">
+        <v>1.35E-2</v>
+      </c>
+      <c r="C3">
+        <v>9.5</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <f>40/F3</f>
+        <v>28.548360476579195</v>
+      </c>
+      <c r="F3">
+        <f>C3^2*B3*1.15</f>
+        <v>1.4011312499999999</v>
+      </c>
+      <c r="G3">
+        <f>0.00143</f>
+        <v>1.4300000000000001E-3</v>
+      </c>
+      <c r="H3">
+        <v>1.3729999999999999E-2</v>
+      </c>
+      <c r="I3">
+        <v>1.028</v>
+      </c>
+      <c r="J3">
+        <v>2.5179999999999998</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3">
+        <v>8.4</v>
+      </c>
+      <c r="M3">
+        <v>6.8</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BC573D-AEF5-48A1-9870-479DF8E5F424}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0.42</v>
+      </c>
+      <c r="B2">
+        <v>1.5499999999999999E-3</v>
+      </c>
+      <c r="C2">
+        <v>24</v>
+      </c>
+      <c r="D2">
+        <v>23</v>
+      </c>
+      <c r="E2">
+        <f>40/F2</f>
+        <v>38.959015116097873</v>
+      </c>
+      <c r="F2">
+        <f>C2^2*B2*1.15</f>
+        <v>1.0267199999999999</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1.7699999999999999E-4</v>
+      </c>
+      <c r="H2">
+        <v>5.8300000000000001E-3</v>
+      </c>
+      <c r="I2">
+        <v>1.101</v>
+      </c>
+      <c r="J2">
+        <v>2.2490000000000001</v>
+      </c>
+      <c r="K2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2">
+        <v>8.4</v>
+      </c>
+      <c r="M2">
+        <v>6.8</v>
+      </c>
+      <c r="N2">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{059866CC-3168-4352-A7B2-396C26867B98}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -2889,7 +3936,199 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CFB3687-AD18-4C77-91B3-5E580DED5488}">
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="C2">
+        <v>14</v>
+      </c>
+      <c r="D2">
+        <v>22</v>
+      </c>
+      <c r="E2">
+        <f>40/F2</f>
+        <v>31.133734958514303</v>
+      </c>
+      <c r="F2">
+        <f>C2^2*B2*1.15</f>
+        <v>1.2847799999999998</v>
+      </c>
+      <c r="G2" s="3">
+        <v>2.52E-4</v>
+      </c>
+      <c r="H2" s="3">
+        <v>7.0499999999999998E-3</v>
+      </c>
+      <c r="I2">
+        <v>1.101</v>
+      </c>
+      <c r="J2">
+        <v>2.2490000000000001</v>
+      </c>
+      <c r="K2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2">
+        <v>13.6</v>
+      </c>
+      <c r="M2">
+        <v>10.3</v>
+      </c>
+      <c r="N2">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1.5</v>
+      </c>
+      <c r="B3">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="C3">
+        <v>11.5</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <f>40/F3</f>
+        <v>28.587662279651664</v>
+      </c>
+      <c r="F3">
+        <f>C3^2*B3*1.15</f>
+        <v>1.3992049999999998</v>
+      </c>
+      <c r="G3" s="3">
+        <v>2.5300000000000002E-4</v>
+      </c>
+      <c r="H3" s="3">
+        <v>8.3499999999999998E-3</v>
+      </c>
+      <c r="I3">
+        <v>1.101</v>
+      </c>
+      <c r="J3">
+        <v>2.2490000000000001</v>
+      </c>
+      <c r="K3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3">
+        <v>13.6</v>
+      </c>
+      <c r="M3">
+        <v>10.3</v>
+      </c>
+      <c r="N3">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="C4">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <f>40/F4</f>
+        <v>22.457779374775424</v>
+      </c>
+      <c r="F4">
+        <f>C4^2*B4*1.15</f>
+        <v>1.78112</v>
+      </c>
+      <c r="G4" s="3">
+        <v>2.23E-4</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1.0189999999999999E-2</v>
+      </c>
+      <c r="I4">
+        <v>1.101</v>
+      </c>
+      <c r="J4">
+        <v>2.2490000000000001</v>
+      </c>
+      <c r="K4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4">
+        <v>13.6</v>
+      </c>
+      <c r="M4">
+        <v>10.3</v>
+      </c>
+      <c r="N4">
+        <v>2.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4084553-0357-4668-80B7-A59E449DE9A2}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -3027,7 +4266,107 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCCAFF9F-57A3-4F2B-A1C5-BDA09AA27FFF}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="C2">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <f>40/F2</f>
+        <v>25.72678157962439</v>
+      </c>
+      <c r="F2">
+        <f>C2^2*B2*1.15</f>
+        <v>1.5548</v>
+      </c>
+      <c r="G2" s="3">
+        <v>2.99E-3</v>
+      </c>
+      <c r="H2" s="3">
+        <v>9.0900000000000009E-3</v>
+      </c>
+      <c r="I2">
+        <v>1.028</v>
+      </c>
+      <c r="J2">
+        <v>2.5179999999999998</v>
+      </c>
+      <c r="K2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2">
+        <v>13.6</v>
+      </c>
+      <c r="M2">
+        <v>10.3</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE769611-9C4A-4D12-ACD1-572EFA17A665}">
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -3219,7 +4558,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04542642-2AB9-4E4E-BC92-700C7AD35014}">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -3956,206 +5295,6 @@
       </c>
       <c r="N16">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2190A832-EF70-43A1-B39D-AE9C42882809}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="C2">
-        <v>25.5</v>
-      </c>
-      <c r="D2">
-        <v>36</v>
-      </c>
-      <c r="E2" s="2">
-        <f>40/F2</f>
-        <v>24.314150987838367</v>
-      </c>
-      <c r="F2" s="5">
-        <f>C2^2*B2*1.15</f>
-        <v>1.6451324999999999</v>
-      </c>
-      <c r="G2" s="3">
-        <v>5.1800000000000001E-4</v>
-      </c>
-      <c r="H2">
-        <v>4.2700000000000004E-3</v>
-      </c>
-      <c r="I2">
-        <v>1.101</v>
-      </c>
-      <c r="J2">
-        <v>2.2490000000000001</v>
-      </c>
-      <c r="K2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L2">
-        <v>13.6</v>
-      </c>
-      <c r="M2">
-        <v>10</v>
-      </c>
-      <c r="N2">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE43545-A402-4460-BE10-D9DDD354CCCC}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B2">
-        <v>4.4999999999999997E-3</v>
-      </c>
-      <c r="C2">
-        <v>20</v>
-      </c>
-      <c r="D2">
-        <v>36</v>
-      </c>
-      <c r="E2">
-        <f>40/F2</f>
-        <v>19.323671497584542</v>
-      </c>
-      <c r="F2">
-        <f>C2^2*B2*1.15</f>
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="G2" s="3">
-        <v>3.81E-3</v>
-      </c>
-      <c r="H2">
-        <v>5.0400000000000002E-3</v>
-      </c>
-      <c r="I2">
-        <v>1.0109999999999999</v>
-      </c>
-      <c r="J2">
-        <v>2.363</v>
-      </c>
-      <c r="K2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2">
-        <v>14.5</v>
-      </c>
-      <c r="M2">
-        <v>12.8</v>
-      </c>
-      <c r="N2">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4268,6 +5407,206 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2190A832-EF70-43A1-B39D-AE9C42882809}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="C2">
+        <v>25.5</v>
+      </c>
+      <c r="D2">
+        <v>36</v>
+      </c>
+      <c r="E2" s="2">
+        <f>40/F2</f>
+        <v>24.314150987838367</v>
+      </c>
+      <c r="F2" s="5">
+        <f>C2^2*B2*1.15</f>
+        <v>1.6451324999999999</v>
+      </c>
+      <c r="G2" s="3">
+        <v>5.1800000000000001E-4</v>
+      </c>
+      <c r="H2">
+        <v>4.2700000000000004E-3</v>
+      </c>
+      <c r="I2">
+        <v>1.101</v>
+      </c>
+      <c r="J2">
+        <v>2.2490000000000001</v>
+      </c>
+      <c r="K2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2">
+        <v>13.6</v>
+      </c>
+      <c r="M2">
+        <v>10</v>
+      </c>
+      <c r="N2">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE43545-A402-4460-BE10-D9DDD354CCCC}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="C2">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>36</v>
+      </c>
+      <c r="E2">
+        <f>40/F2</f>
+        <v>19.323671497584542</v>
+      </c>
+      <c r="F2">
+        <f>C2^2*B2*1.15</f>
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="G2" s="3">
+        <v>3.81E-3</v>
+      </c>
+      <c r="H2">
+        <v>5.0400000000000002E-3</v>
+      </c>
+      <c r="I2">
+        <v>1.0109999999999999</v>
+      </c>
+      <c r="J2">
+        <v>2.363</v>
+      </c>
+      <c r="K2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2">
+        <v>14.5</v>
+      </c>
+      <c r="M2">
+        <v>12.8</v>
+      </c>
+      <c r="N2">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47093BEB-5A01-48EC-839D-26C22180712E}">
   <dimension ref="A1:N2"/>
@@ -4373,6 +5712,778 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807162F9-D51A-4370-A870-1472E8FD2D03}">
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="B2">
+        <v>8.4999999999999995E-4</v>
+      </c>
+      <c r="C2">
+        <v>38</v>
+      </c>
+      <c r="D2">
+        <v>45</v>
+      </c>
+      <c r="E2">
+        <f>40/F2</f>
+        <v>28.338446061310236</v>
+      </c>
+      <c r="F2">
+        <f>C2^2*B2*1.15</f>
+        <v>1.4115099999999996</v>
+      </c>
+      <c r="G2">
+        <f>0.00000957</f>
+        <v>9.5699999999999999E-6</v>
+      </c>
+      <c r="H2">
+        <v>5.1599999999999997E-3</v>
+      </c>
+      <c r="I2">
+        <v>1.254</v>
+      </c>
+      <c r="J2">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2">
+        <v>5.5</v>
+      </c>
+      <c r="M2">
+        <v>5.7</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
+        <v>0.33</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1.8E-3</v>
+      </c>
+      <c r="C3">
+        <v>28.5</v>
+      </c>
+      <c r="D3">
+        <v>32</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E8" si="0">40/F3</f>
+        <v>23.790300397149334</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F8" si="1">C3^2*B3*1.15</f>
+        <v>1.6813574999999996</v>
+      </c>
+      <c r="G3">
+        <f>0.0000096</f>
+        <v>9.5999999999999996E-6</v>
+      </c>
+      <c r="H3">
+        <v>6.7799999999999996E-3</v>
+      </c>
+      <c r="I3">
+        <v>1.254</v>
+      </c>
+      <c r="J3">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>5.5</v>
+      </c>
+      <c r="M3">
+        <v>5.7</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>0.36</v>
+      </c>
+      <c r="B4">
+        <v>2E-3</v>
+      </c>
+      <c r="C4">
+        <v>27</v>
+      </c>
+      <c r="D4">
+        <v>29</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>23.856384564919189</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>1.6766999999999999</v>
+      </c>
+      <c r="G4">
+        <f>0.00000983</f>
+        <v>9.8300000000000008E-6</v>
+      </c>
+      <c r="H4">
+        <v>6.9899999999999997E-3</v>
+      </c>
+      <c r="I4">
+        <v>1.254</v>
+      </c>
+      <c r="J4">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4">
+        <v>5.5</v>
+      </c>
+      <c r="M4">
+        <v>5.7</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>0.47</v>
+      </c>
+      <c r="B5">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="C5">
+        <v>24</v>
+      </c>
+      <c r="D5">
+        <v>26</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>24.154589371980677</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>1.6559999999999999</v>
+      </c>
+      <c r="G5">
+        <f>0.00000883</f>
+        <v>8.8300000000000002E-6</v>
+      </c>
+      <c r="H5">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="I5">
+        <v>1.254</v>
+      </c>
+      <c r="J5">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5">
+        <v>5.5</v>
+      </c>
+      <c r="M5">
+        <v>5.7</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="B6">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>23.95496466642712</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>1.6697999999999997</v>
+      </c>
+      <c r="G6">
+        <f>0.00000921</f>
+        <v>9.2099999999999999E-6</v>
+      </c>
+      <c r="H6">
+        <v>1.03E-2</v>
+      </c>
+      <c r="I6">
+        <v>1.254</v>
+      </c>
+      <c r="J6">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6">
+        <v>5.5</v>
+      </c>
+      <c r="M6">
+        <v>5.7</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="B7">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="C7">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>23.375032053012696</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>1.7112276000000004</v>
+      </c>
+      <c r="G7" s="3">
+        <v>3.36E-6</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1.8890000000000001E-2</v>
+      </c>
+      <c r="I7">
+        <v>1.254</v>
+      </c>
+      <c r="J7">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7">
+        <v>4.5</v>
+      </c>
+      <c r="M7">
+        <v>4.5</v>
+      </c>
+      <c r="N7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>9.5</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>23.661638568470867</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>1.6904999999999999</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3.2799999999999999E-6</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2.3609999999999999E-2</v>
+      </c>
+      <c r="I8">
+        <v>1.254</v>
+      </c>
+      <c r="J8">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8">
+        <v>4.5</v>
+      </c>
+      <c r="M8">
+        <v>4.5</v>
+      </c>
+      <c r="N8">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FDF93FE-8DA2-4394-A0F2-323BE915373C}">
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="B2">
+        <v>8.4999999999999995E-4</v>
+      </c>
+      <c r="C2">
+        <v>38</v>
+      </c>
+      <c r="D2">
+        <v>45</v>
+      </c>
+      <c r="E2">
+        <f>40/F2</f>
+        <v>28.338446061310236</v>
+      </c>
+      <c r="F2">
+        <f>C2^2*B2*1.15</f>
+        <v>1.4115099999999996</v>
+      </c>
+      <c r="G2">
+        <f>0.00000957</f>
+        <v>9.5699999999999999E-6</v>
+      </c>
+      <c r="H2">
+        <v>5.1599999999999997E-3</v>
+      </c>
+      <c r="I2">
+        <v>1.254</v>
+      </c>
+      <c r="J2">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2">
+        <v>5.5</v>
+      </c>
+      <c r="M2">
+        <v>5.7</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
+        <v>0.33</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1.8E-3</v>
+      </c>
+      <c r="C3">
+        <v>28.5</v>
+      </c>
+      <c r="D3">
+        <v>32</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E8" si="0">40/F3</f>
+        <v>23.790300397149334</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F8" si="1">C3^2*B3*1.15</f>
+        <v>1.6813574999999996</v>
+      </c>
+      <c r="G3">
+        <f>0.0000096</f>
+        <v>9.5999999999999996E-6</v>
+      </c>
+      <c r="H3">
+        <v>6.7799999999999996E-3</v>
+      </c>
+      <c r="I3">
+        <v>1.254</v>
+      </c>
+      <c r="J3">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>5.5</v>
+      </c>
+      <c r="M3">
+        <v>5.7</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>0.36</v>
+      </c>
+      <c r="B4">
+        <v>2E-3</v>
+      </c>
+      <c r="C4">
+        <v>27</v>
+      </c>
+      <c r="D4">
+        <v>29</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>23.856384564919189</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>1.6766999999999999</v>
+      </c>
+      <c r="G4">
+        <f>0.00000983</f>
+        <v>9.8300000000000008E-6</v>
+      </c>
+      <c r="H4">
+        <v>6.9899999999999997E-3</v>
+      </c>
+      <c r="I4">
+        <v>1.254</v>
+      </c>
+      <c r="J4">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4">
+        <v>5.5</v>
+      </c>
+      <c r="M4">
+        <v>5.7</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>0.47</v>
+      </c>
+      <c r="B5">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="C5">
+        <v>24</v>
+      </c>
+      <c r="D5">
+        <v>26</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>24.154589371980677</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>1.6559999999999999</v>
+      </c>
+      <c r="G5">
+        <f>0.00000883</f>
+        <v>8.8300000000000002E-6</v>
+      </c>
+      <c r="H5">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="I5">
+        <v>1.254</v>
+      </c>
+      <c r="J5">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5">
+        <v>5.5</v>
+      </c>
+      <c r="M5">
+        <v>5.7</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="B6">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>23.95496466642712</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>1.6697999999999997</v>
+      </c>
+      <c r="G6">
+        <f>0.00000921</f>
+        <v>9.2099999999999999E-6</v>
+      </c>
+      <c r="H6">
+        <v>1.03E-2</v>
+      </c>
+      <c r="I6">
+        <v>1.254</v>
+      </c>
+      <c r="J6">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6">
+        <v>5.5</v>
+      </c>
+      <c r="M6">
+        <v>5.7</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="B7">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="C7">
+        <v>17.8</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>24.949937949504321</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>1.6032104</v>
+      </c>
+      <c r="G7" s="3">
+        <v>4.7999999999999998E-6</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1.4030000000000001E-2</v>
+      </c>
+      <c r="I7">
+        <v>1.254</v>
+      </c>
+      <c r="J7">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7">
+        <v>4.5</v>
+      </c>
+      <c r="M7">
+        <v>4.5</v>
+      </c>
+      <c r="N7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="C8">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>11.6</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>25.764895330112722</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>1.5525</v>
+      </c>
+      <c r="G8" s="3">
+        <v>5.31E-6</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1.5869999999999999E-2</v>
+      </c>
+      <c r="I8">
+        <v>1.254</v>
+      </c>
+      <c r="J8">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="K8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8">
+        <v>4.5</v>
+      </c>
+      <c r="M8">
+        <v>4.5</v>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BBB5906-5371-47ED-8BD9-50A2EE17B788}">
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -4569,7 +6680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4706258-9C79-430A-ADA3-56A4A12710BB}">
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -4766,9 +6877,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B931419B-A406-4BFE-8A46-5F910D217C80}">
-  <dimension ref="A1:N11"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9FA3793-097F-426B-B197-F396D592293A}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -4824,28 +6935,27 @@
         <v>0.15</v>
       </c>
       <c r="B2">
-        <v>8.4999999999999995E-4</v>
+        <v>1.5E-3</v>
       </c>
       <c r="C2">
-        <v>38</v>
+        <v>24.5</v>
       </c>
       <c r="D2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E2">
         <f>40/F2</f>
-        <v>28.338446061310236</v>
+        <v>38.631246642401415</v>
       </c>
       <c r="F2">
         <f>C2^2*B2*1.15</f>
-        <v>1.4115099999999996</v>
-      </c>
-      <c r="G2">
-        <f>0.00000957</f>
-        <v>9.5699999999999999E-6</v>
+        <v>1.03543125</v>
+      </c>
+      <c r="G2" s="3">
+        <v>7.7840000000000004E-6</v>
       </c>
       <c r="H2">
-        <v>5.1599999999999997E-3</v>
+        <v>4.5869999999999999E-3</v>
       </c>
       <c r="I2">
         <v>1.254</v>
@@ -4854,7 +6964,7 @@
         <v>2.3260000000000001</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L2">
         <v>5.5</v>
@@ -4863,774 +6973,7 @@
         <v>5.7</v>
       </c>
       <c r="N2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
-        <v>0.33</v>
-      </c>
-      <c r="B3" s="3">
-        <v>1.8E-3</v>
-      </c>
-      <c r="C3">
-        <v>28.5</v>
-      </c>
-      <c r="D3">
-        <v>32</v>
-      </c>
-      <c r="E3">
-        <f t="shared" ref="E3:E11" si="0">40/F3</f>
-        <v>23.790300397149334</v>
-      </c>
-      <c r="F3">
-        <f t="shared" ref="F3:F11" si="1">C3^2*B3*1.15</f>
-        <v>1.6813574999999996</v>
-      </c>
-      <c r="G3">
-        <f>0.0000096</f>
-        <v>9.5999999999999996E-6</v>
-      </c>
-      <c r="H3">
-        <v>6.7799999999999996E-3</v>
-      </c>
-      <c r="I3">
-        <v>1.254</v>
-      </c>
-      <c r="J3">
-        <v>2.3260000000000001</v>
-      </c>
-      <c r="K3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>5.5</v>
-      </c>
-      <c r="M3">
-        <v>5.7</v>
-      </c>
-      <c r="N3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
-        <v>0.36</v>
-      </c>
-      <c r="B4">
-        <v>2E-3</v>
-      </c>
-      <c r="C4">
-        <v>27</v>
-      </c>
-      <c r="D4">
-        <v>29</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="0"/>
-        <v>23.856384564919189</v>
-      </c>
-      <c r="F4">
-        <f t="shared" si="1"/>
-        <v>1.6766999999999999</v>
-      </c>
-      <c r="G4">
-        <f>0.00000983</f>
-        <v>9.8300000000000008E-6</v>
-      </c>
-      <c r="H4">
-        <v>6.9899999999999997E-3</v>
-      </c>
-      <c r="I4">
-        <v>1.254</v>
-      </c>
-      <c r="J4">
-        <v>2.3260000000000001</v>
-      </c>
-      <c r="K4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4">
-        <v>5.5</v>
-      </c>
-      <c r="M4">
-        <v>5.7</v>
-      </c>
-      <c r="N4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>0.47</v>
-      </c>
-      <c r="B5">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="C5">
-        <v>24</v>
-      </c>
-      <c r="D5">
-        <v>26</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="0"/>
-        <v>24.154589371980677</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="1"/>
-        <v>1.6559999999999999</v>
-      </c>
-      <c r="G5">
-        <f>0.00000883</f>
-        <v>8.8300000000000002E-6</v>
-      </c>
-      <c r="H5">
-        <v>9.2999999999999992E-3</v>
-      </c>
-      <c r="I5">
-        <v>1.254</v>
-      </c>
-      <c r="J5">
-        <v>2.3260000000000001</v>
-      </c>
-      <c r="K5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5">
-        <v>5.5</v>
-      </c>
-      <c r="M5">
-        <v>5.7</v>
-      </c>
-      <c r="N5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="B6">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="C6">
-        <v>22</v>
-      </c>
-      <c r="D6">
-        <v>24</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="0"/>
-        <v>23.95496466642712</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="1"/>
-        <v>1.6697999999999997</v>
-      </c>
-      <c r="G6">
-        <f>0.00000921</f>
-        <v>9.2099999999999999E-6</v>
-      </c>
-      <c r="H6">
-        <v>1.03E-2</v>
-      </c>
-      <c r="I6">
-        <v>1.254</v>
-      </c>
-      <c r="J6">
-        <v>2.3260000000000001</v>
-      </c>
-      <c r="K6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6">
-        <v>5.5</v>
-      </c>
-      <c r="M6">
-        <v>5.7</v>
-      </c>
-      <c r="N6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
-        <v>0.68</v>
-      </c>
-      <c r="B7">
-        <v>3.8E-3</v>
-      </c>
-      <c r="C7">
-        <v>19.5</v>
-      </c>
-      <c r="D7">
-        <v>21.5</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="0"/>
-        <v>24.07184241368364</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="1"/>
-        <v>1.6616924999999998</v>
-      </c>
-      <c r="G7">
-        <f>0.00000871</f>
-        <v>8.7099999999999996E-6</v>
-      </c>
-      <c r="H7">
-        <v>1.0200000000000001E-2</v>
-      </c>
-      <c r="I7">
-        <v>1.254</v>
-      </c>
-      <c r="J7">
-        <v>2.3260000000000001</v>
-      </c>
-      <c r="K7" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7">
-        <v>5.5</v>
-      </c>
-      <c r="M7">
-        <v>5.7</v>
-      </c>
-      <c r="N7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="C8">
-        <v>17</v>
-      </c>
-      <c r="D8">
-        <v>18</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="0"/>
-        <v>24.071009477959983</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="1"/>
-        <v>1.6617499999999998</v>
-      </c>
-      <c r="G8">
-        <f>0.00000872</f>
-        <v>8.7199999999999995E-6</v>
-      </c>
-      <c r="H8">
-        <v>1.2200000000000001E-2</v>
-      </c>
-      <c r="I8">
-        <v>1.254</v>
-      </c>
-      <c r="J8">
-        <v>2.3260000000000001</v>
-      </c>
-      <c r="K8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8">
-        <v>5.5</v>
-      </c>
-      <c r="M8">
-        <v>5.7</v>
-      </c>
-      <c r="N8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="B9">
-        <v>7.1999999999999998E-3</v>
-      </c>
-      <c r="C9">
-        <v>14</v>
-      </c>
-      <c r="D9">
-        <v>15</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="0"/>
-        <v>24.647540175490487</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="1"/>
-        <v>1.6228799999999999</v>
-      </c>
-      <c r="G9">
-        <f>0.000008982</f>
-        <v>8.9819999999999997E-6</v>
-      </c>
-      <c r="H9">
-        <v>1.5900000000000001E-2</v>
-      </c>
-      <c r="I9">
-        <v>1.254</v>
-      </c>
-      <c r="J9">
-        <v>2.3260000000000001</v>
-      </c>
-      <c r="K9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9">
-        <v>5.5</v>
-      </c>
-      <c r="M9">
-        <v>5.7</v>
-      </c>
-      <c r="N9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B10">
-        <v>9.7999999999999997E-3</v>
-      </c>
-      <c r="C10">
-        <v>12</v>
-      </c>
-      <c r="D10">
-        <v>11</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="0"/>
-        <v>24.647540175490487</v>
-      </c>
-      <c r="F10">
-        <f t="shared" si="1"/>
-        <v>1.6228799999999999</v>
-      </c>
-      <c r="G10">
-        <f>0.00000891</f>
-        <v>8.9099999999999994E-6</v>
-      </c>
-      <c r="H10">
-        <v>1.9599999999999999E-2</v>
-      </c>
-      <c r="I10">
-        <v>1.254</v>
-      </c>
-      <c r="J10">
-        <v>2.3260000000000001</v>
-      </c>
-      <c r="K10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10">
-        <v>5.5</v>
-      </c>
-      <c r="M10">
-        <v>5.7</v>
-      </c>
-      <c r="N10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="B11">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-      <c r="D11">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
-        <v>23.188405797101453</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="1"/>
-        <v>1.7249999999999999</v>
-      </c>
-      <c r="G11">
-        <f>0.00000885</f>
-        <v>8.85E-6</v>
-      </c>
-      <c r="H11">
-        <v>2.3199999999999998E-2</v>
-      </c>
-      <c r="I11">
-        <v>1.254</v>
-      </c>
-      <c r="J11">
-        <v>2.3260000000000001</v>
-      </c>
-      <c r="K11" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11">
-        <v>5.5</v>
-      </c>
-      <c r="M11">
-        <v>5.7</v>
-      </c>
-      <c r="N11">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A5FAB1-3D42-4172-B790-7D8771165FE4}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="C2">
-        <v>8.5</v>
-      </c>
-      <c r="D2">
-        <v>11</v>
-      </c>
-      <c r="E2">
-        <f>40/F2</f>
-        <v>37.032322273784594</v>
-      </c>
-      <c r="F2">
-        <f>C2^2*B2*1.15</f>
-        <v>1.0801374999999998</v>
-      </c>
-      <c r="G2">
-        <f>0.000669</f>
-        <v>6.69E-4</v>
-      </c>
-      <c r="H2">
-        <v>1.4370000000000001E-2</v>
-      </c>
-      <c r="I2">
-        <v>1.028</v>
-      </c>
-      <c r="J2">
-        <v>2.5179999999999998</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2">
-        <v>7</v>
-      </c>
-      <c r="M2">
-        <v>4.7</v>
-      </c>
-      <c r="N2">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F45A2FD-4FF8-4DE7-9D64-03112843A7F5}">
-  <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="B2">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="C2">
-        <v>11</v>
-      </c>
-      <c r="D2">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2">
-        <f t="shared" ref="E2:E5" si="0">40/F2</f>
-        <v>35.932446999640675</v>
-      </c>
-      <c r="F2" s="1">
-        <f t="shared" ref="F2:F5" si="1">C2^2*B2*1.15</f>
-        <v>1.1132</v>
-      </c>
-      <c r="G2">
-        <f>0.000714</f>
-        <v>7.1400000000000001E-4</v>
-      </c>
-      <c r="H2">
-        <v>9.5600000000000008E-3</v>
-      </c>
-      <c r="I2">
-        <v>1.028</v>
-      </c>
-      <c r="J2">
-        <v>2.5179999999999998</v>
-      </c>
-      <c r="K2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2">
-        <v>7</v>
-      </c>
-      <c r="M2">
-        <v>4.7</v>
-      </c>
-      <c r="N2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>0.68</v>
-      </c>
-      <c r="B3">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="C3">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>11.5</v>
-      </c>
-      <c r="E3" s="2">
-        <f t="shared" si="0"/>
-        <v>35.932446999640675</v>
-      </c>
-      <c r="F3" s="1">
-        <f t="shared" si="1"/>
-        <v>1.1132</v>
-      </c>
-      <c r="G3">
-        <f>0.000715</f>
-        <v>7.1500000000000003E-4</v>
-      </c>
-      <c r="H3">
-        <v>1.06E-2</v>
-      </c>
-      <c r="I3">
-        <v>1.028</v>
-      </c>
-      <c r="J3">
-        <v>2.5179999999999998</v>
-      </c>
-      <c r="K3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>4.7</v>
-      </c>
-      <c r="N3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>1.0500000000000001E-2</v>
-      </c>
-      <c r="C4">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="D4">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2">
-        <f t="shared" si="0"/>
-        <v>34.492184502144113</v>
-      </c>
-      <c r="F4" s="1">
-        <f t="shared" si="1"/>
-        <v>1.1596830000000002</v>
-      </c>
-      <c r="G4">
-        <f>0.000642</f>
-        <v>6.4199999999999999E-4</v>
-      </c>
-      <c r="H4">
-        <v>1.465E-2</v>
-      </c>
-      <c r="I4">
-        <v>1.028</v>
-      </c>
-      <c r="J4">
-        <v>2.5179999999999998</v>
-      </c>
-      <c r="K4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4">
-        <v>7</v>
-      </c>
-      <c r="M4">
-        <v>4.7</v>
-      </c>
-      <c r="N4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1.5</v>
-      </c>
-      <c r="B5">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="C5">
-        <v>7.8</v>
-      </c>
-      <c r="D5">
-        <v>8.6</v>
-      </c>
-      <c r="E5" s="2">
-        <f t="shared" si="0"/>
-        <v>33.629779842646258</v>
-      </c>
-      <c r="F5" s="1">
-        <f t="shared" si="1"/>
-        <v>1.189422</v>
-      </c>
-      <c r="G5">
-        <f>0.000657</f>
-        <v>6.5700000000000003E-4</v>
-      </c>
-      <c r="H5">
-        <v>1.562E-2</v>
-      </c>
-      <c r="I5">
-        <v>1.028</v>
-      </c>
-      <c r="J5">
-        <v>2.5179999999999998</v>
-      </c>
-      <c r="K5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
-        <v>4.7</v>
-      </c>
-      <c r="N5">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>
